--- a/2026/FLORES DE ESTRADA/ENERO/PRORRATEO Enero Estrada.xlsx
+++ b/2026/FLORES DE ESTRADA/ENERO/PRORRATEO Enero Estrada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\FLORES DE ESTRADA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABF42E5-4B5C-466E-8632-A1CB2AED5D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E90E574-F13F-4E4B-B3B4-054BE74341BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -271,10 +271,10 @@
     <t>NN</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 15/01  LIQUIDACION : DICIEMBRE</t>
-  </si>
-  <si>
     <t>Romina</t>
+  </si>
+  <si>
+    <t>EXPENSAS - VENCIMIENTO 16/02 - PERIODO ENERO</t>
   </si>
 </sst>
 </file>
@@ -288,7 +288,7 @@
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,6 +409,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -612,7 +619,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -726,6 +733,7 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -747,7 +755,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1107,22 +1115,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70"/>
+      <c r="A1" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="71"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1155,13 +1163,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="66">
+      <c r="J4" s="67">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1287,24 +1295,21 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F11" s="5">
-        <v>68600.000000000015</v>
-      </c>
-      <c r="G11" s="72">
-        <f>F11</f>
-        <v>68600.000000000015</v>
-      </c>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="G11" s="65"/>
       <c r="H11" s="8">
         <f>F11-G11</f>
-        <v>0</v>
+        <v>49254.983260000015</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="9">
         <f>H11*8.8%</f>
-        <v>0</v>
+        <v>4334.4385268800015</v>
       </c>
       <c r="K11" s="44">
         <f>H11+J11</f>
-        <v>0</v>
+        <v>53589.421786880019</v>
       </c>
       <c r="L11" s="5">
         <f>C7*E11/100</f>
@@ -1316,7 +1321,7 @@
       </c>
       <c r="N11" s="44">
         <f>K11+L11+M11</f>
-        <v>49254.983260000015</v>
+        <v>102844.40504688004</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1336,23 +1341,23 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>1399609.5687795526</v>
-      </c>
-      <c r="G12" s="72"/>
+        <v>1561877.6363181532</v>
+      </c>
+      <c r="G12" s="65"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>1399609.5687795526</v>
+        <v>1561877.6363181532</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>123165.64205260064</v>
+        <v>137445.23199599748</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>1522775.2108321532</v>
+        <v>1699322.8683141507</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
@@ -1364,7 +1369,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>1561877.6363181532</v>
+        <v>1738425.2938001507</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1384,11 +1389,11 @@
         <v>4</v>
       </c>
       <c r="F13" s="5">
-        <v>56000</v>
-      </c>
-      <c r="G13" s="72">
+        <v>40208.149600000004</v>
+      </c>
+      <c r="G13" s="73">
         <f>F13</f>
-        <v>56000</v>
+        <v>40208.149600000004</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="0"/>
@@ -1436,11 +1441,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F14" s="5">
-        <v>68600.000000000015</v>
-      </c>
-      <c r="G14" s="72">
+        <v>49254.983260000015</v>
+      </c>
+      <c r="G14" s="73">
         <f>F14</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
@@ -1487,11 +1492,11 @@
         <v>3.89</v>
       </c>
       <c r="F15" s="5">
-        <v>54460</v>
-      </c>
-      <c r="G15" s="72">
+        <v>39102.425486</v>
+      </c>
+      <c r="G15" s="73">
         <f>F15</f>
-        <v>54460</v>
+        <v>39102.425486</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
@@ -1533,31 +1538,32 @@
         <v>9</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3">
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>192224.7862087437</v>
-      </c>
-      <c r="G16" s="72">
-        <v>56000</v>
+        <v>188420.71699511315</v>
+      </c>
+      <c r="G16" s="73">
+        <f>40208-10450</f>
+        <v>29758</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>136224.7862087437</v>
+        <v>158662.71699511315</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>11987.781186369446</v>
+        <v>13962.319095569959</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>148212.56739511315</v>
+        <v>172625.0360906831</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
@@ -1569,7 +1575,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="2"/>
-        <v>188420.71699511315</v>
+        <v>212833.18569068311</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1589,11 +1595,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F17" s="5">
-        <v>68600.000000000015</v>
-      </c>
-      <c r="G17" s="72">
+        <v>49254.983260000015</v>
+      </c>
+      <c r="G17" s="73">
         <f>F17</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
@@ -1638,11 +1644,11 @@
         <v>3.89</v>
       </c>
       <c r="F18" s="5">
-        <v>54460</v>
-      </c>
-      <c r="G18" s="72">
-        <f t="shared" ref="G17:G21" si="3">F18</f>
-        <v>54460</v>
+        <v>39102.425486</v>
+      </c>
+      <c r="G18" s="73">
+        <f t="shared" ref="G18:G19" si="3">F18</f>
+        <v>39102.425486</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="0"/>
@@ -1689,11 +1695,11 @@
         <v>4</v>
       </c>
       <c r="F19" s="5">
-        <v>56000</v>
-      </c>
-      <c r="G19" s="72">
+        <v>40208.149600000004</v>
+      </c>
+      <c r="G19" s="73">
         <f t="shared" si="3"/>
-        <v>56000</v>
+        <v>40208.149600000004</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="0"/>
@@ -1738,26 +1744,23 @@
         <v>12.66</v>
       </c>
       <c r="F20" s="5">
-        <v>177240</v>
-      </c>
-      <c r="G20" s="72">
-        <f>F20</f>
-        <v>177240</v>
-      </c>
+        <v>127258.79348400002</v>
+      </c>
+      <c r="G20" s="65"/>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>127258.79348400002</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11198.773826592003</v>
       </c>
       <c r="K20" s="44">
         <f>H20+J20+I20</f>
-        <v>0</v>
+        <v>138457.56731059201</v>
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
@@ -1769,7 +1772,7 @@
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>127258.79348400002</v>
+        <v>265716.36079459207</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1789,26 +1792,23 @@
         <v>7.75</v>
       </c>
       <c r="F21" s="5">
-        <v>108500</v>
-      </c>
-      <c r="G21" s="72">
-        <f>F21</f>
-        <v>108500</v>
-      </c>
+        <v>77903.289850000016</v>
+      </c>
+      <c r="G21" s="65"/>
       <c r="H21" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>77903.289850000016</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6855.4895068000023</v>
       </c>
       <c r="K21" s="44">
         <f>H21+J21+I21</f>
-        <v>0</v>
+        <v>84758.77935680002</v>
       </c>
       <c r="L21" s="5">
         <f>C7*E21/100</f>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="N21" s="44">
         <f t="shared" si="2"/>
-        <v>77903.289850000016</v>
+        <v>162662.06920680002</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1838,26 +1838,23 @@
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>343991.16416000004</v>
-      </c>
-      <c r="G22" s="72">
-        <f>F22</f>
-        <v>343991.16416000004</v>
-      </c>
+        <v>75490.800874000008</v>
+      </c>
+      <c r="G22" s="65"/>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>75490.800874000008</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6643.190476912001</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="5">H22+J22+I22</f>
-        <v>0</v>
+        <v>82133.991350912009</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
@@ -1869,7 +1866,7 @@
       </c>
       <c r="N22" s="44">
         <f t="shared" si="2"/>
-        <v>75490.800874000008</v>
+        <v>157624.79222491203</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1887,23 +1884,23 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>346123.80555998289</v>
-      </c>
-      <c r="G23" s="72"/>
+        <v>421314.26687926141</v>
+      </c>
+      <c r="G23" s="65"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>346123.80555998289</v>
+        <v>421314.26687926141</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>30458.894889278497</v>
+        <v>37075.655485375006</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>376582.70044926141</v>
+        <v>458389.92236463644</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
@@ -1915,7 +1912,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>421314.26687926141</v>
+        <v>503121.48879463645</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1933,26 +1930,23 @@
         <v>6.17</v>
       </c>
       <c r="F24" s="5">
-        <v>86380</v>
-      </c>
-      <c r="G24" s="72">
-        <f>F24</f>
-        <v>86380</v>
-      </c>
+        <v>62021.070758000009</v>
+      </c>
+      <c r="G24" s="65"/>
       <c r="H24" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>62021.070758000009</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>
       </c>
       <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5457.8542267040011</v>
       </c>
       <c r="K24" s="44">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>67478.924984704005</v>
       </c>
       <c r="L24" s="5">
         <f>C7*E24/100</f>
@@ -1964,7 +1958,7 @@
       </c>
       <c r="N24" s="44">
         <f t="shared" si="2"/>
-        <v>62021.070758000009</v>
+        <v>129499.99574270402</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -1984,25 +1978,25 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>621792.44797249511</v>
-      </c>
-      <c r="G25" s="72">
+        <v>653459.26182407467</v>
+      </c>
+      <c r="G25" s="73">
         <v>62301</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>559491.44797249511</v>
+        <v>591158.26182407467</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>49235.247421579574</v>
+        <v>52021.927040518574</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>608726.69539407466</v>
+        <v>643180.18886459328</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
@@ -2014,7 +2008,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>653459.26182407467</v>
+        <v>687912.75529459328</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2034,25 +2028,25 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>1763640.4643486661</v>
-      </c>
-      <c r="G26" s="72">
-        <v>128661</v>
+        <v>1871236.8809173489</v>
+      </c>
+      <c r="G26" s="73">
+        <v>92379</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>1634979.4643486661</v>
+        <v>1778857.8809173489</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>143878.19286268263</v>
+        <v>156539.49352072671</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>1778857.6572113489</v>
+        <v>1935397.3744380756</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
@@ -2064,7 +2058,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>1871236.8809173489</v>
+        <v>2027776.5981440756</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2084,26 +2078,23 @@
         <v>1.18</v>
       </c>
       <c r="F27" s="5">
-        <v>16521</v>
-      </c>
-      <c r="G27" s="72">
-        <f>F27</f>
-        <v>16521</v>
-      </c>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G27" s="65"/>
       <c r="H27" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="I27" s="5">
         <v>0</v>
       </c>
       <c r="J27" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1043.8915636160002</v>
       </c>
       <c r="K27" s="44">
         <f t="shared" ref="K27:K34" si="6">H27+J27+I27</f>
-        <v>0</v>
+        <v>12906.295695616001</v>
       </c>
       <c r="L27" s="5">
         <f>C7*E27/100+1</f>
@@ -2115,7 +2106,7 @@
       </c>
       <c r="N27" s="44">
         <f>K27+L27+M27</f>
-        <v>11862.404132000001</v>
+        <v>24768.699827616001</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2133,23 +2124,23 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>220658.18368703971</v>
-      </c>
-      <c r="G28" s="72"/>
+        <v>251938.50798349921</v>
+      </c>
+      <c r="G28" s="65"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>220658.18368703971</v>
+        <v>251938.50798349921</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>19417.920164459498</v>
+        <v>22170.588702547931</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="6"/>
-        <v>240076.10385149921</v>
+        <v>274109.09668604715</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
@@ -2161,7 +2152,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="7">K28+L28+M28</f>
-        <v>251938.50798349921</v>
+        <v>285971.50081804715</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2179,23 +2170,23 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>220658.18368703971</v>
-      </c>
-      <c r="G29" s="72"/>
+        <v>251938.50798349921</v>
+      </c>
+      <c r="G29" s="65"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>220658.18368703971</v>
+        <v>251938.50798349921</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>19417.920164459498</v>
+        <v>22170.588702547931</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="6"/>
-        <v>240076.10385149921</v>
+        <v>274109.09668604715</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
@@ -2207,7 +2198,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="7"/>
-        <v>251938.50798349921</v>
+        <v>285971.50081804715</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2225,11 +2216,11 @@
         <v>1.18</v>
       </c>
       <c r="F30" s="5">
-        <v>16521</v>
-      </c>
-      <c r="G30" s="72">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G30" s="73">
         <f>F30</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
@@ -2274,26 +2265,23 @@
         <v>1.18</v>
       </c>
       <c r="F31" s="5">
-        <v>16521</v>
-      </c>
-      <c r="G31" s="72">
-        <f>F31</f>
-        <v>16521</v>
-      </c>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G31" s="65"/>
       <c r="H31" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="I31" s="5">
         <v>0</v>
       </c>
       <c r="J31" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1043.8915636160002</v>
       </c>
       <c r="K31" s="44">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12906.295695616001</v>
       </c>
       <c r="L31" s="5">
         <f>C7*E31/100+1</f>
@@ -2305,7 +2293,7 @@
       </c>
       <c r="N31" s="44">
         <f>K31+L31+M31</f>
-        <v>11862.404132000001</v>
+        <v>24768.699827616001</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2323,11 +2311,11 @@
         <v>1.18</v>
       </c>
       <c r="F32" s="5">
-        <v>16521</v>
-      </c>
-      <c r="G32" s="72">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G32" s="73">
         <f>F32</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="0"/>
@@ -2372,23 +2360,23 @@
         <v>1.18</v>
       </c>
       <c r="F33" s="5">
-        <v>34495.847999999998</v>
-      </c>
-      <c r="G33" s="72"/>
+        <v>49393.886756</v>
+      </c>
+      <c r="G33" s="65"/>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
-        <v>34495.847999999998</v>
+        <v>49393.886756</v>
       </c>
       <c r="I33" s="5">
         <v>0</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="1"/>
-        <v>3035.6346240000003</v>
+        <v>4346.6620345280007</v>
       </c>
       <c r="K33" s="44">
         <f t="shared" si="6"/>
-        <v>37531.482623999997</v>
+        <v>53740.548790528002</v>
       </c>
       <c r="L33" s="5">
         <f>C7*E33/100+1</f>
@@ -2400,7 +2388,7 @@
       </c>
       <c r="N33" s="44">
         <f>K33+L33+M33</f>
-        <v>49393.886756</v>
+        <v>65602.952922527998</v>
       </c>
       <c r="O33" s="59"/>
     </row>
@@ -2419,26 +2407,23 @@
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>54052.482623999997</v>
-      </c>
-      <c r="G34" s="72">
-        <f>F34</f>
-        <v>54052.482623999997</v>
-      </c>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G34" s="65"/>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1043.8915636160002</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12906.295695616001</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
@@ -2450,15 +2435,15 @@
       </c>
       <c r="N34" s="44">
         <f t="shared" si="7"/>
-        <v>11862.404132000001</v>
+        <v>24768.699827616001</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="65"/>
-      <c r="C35" s="65"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2466,15 +2451,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>6062170.9350275202</v>
+        <v>5957951.7412349507</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1509929.6467840001</v>
+        <v>465293.924956</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>4552241.2882435201</v>
+        <v>5492657.8162789503</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2482,7 +2467,7 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>400597.23336542974</v>
+        <v>483353.88783254754</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
@@ -2495,7 +2480,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>5957951.7412349507</v>
+        <v>6981124.9237374971</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3271,11 +3256,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>
